--- a/artfynd/A 34410-2026 artfynd.xlsx
+++ b/artfynd/A 34410-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136293902</v>
       </c>
       <c r="B2" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>136293903</v>
       </c>
       <c r="B3" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>136293904</v>
       </c>
       <c r="B4" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>136293905</v>
       </c>
       <c r="B5" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>136293906</v>
       </c>
       <c r="B6" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>136293908</v>
       </c>
       <c r="B7" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>136293909</v>
       </c>
       <c r="B8" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
